--- a/public/post/drafts/weekly-recap/2025Lillehammer/men_weekend.xlsx
+++ b/public/post/drafts/weekly-recap/2025Lillehammer/men_weekend.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
   <si>
     <t xml:space="preserve">Skier</t>
   </si>
@@ -44,19 +44,127 @@
     <t xml:space="preserve">Norway</t>
   </si>
   <si>
+    <t xml:space="preserve">Martin Løwstrøm Nyenget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simen Hegstad Krüger</t>
+  </si>
+  <si>
     <t xml:space="preserve">Johannes Høsflot Klæbo</t>
   </si>
   <si>
-    <t xml:space="preserve">Martin Løwstrøm Nyenget</t>
+    <t xml:space="preserve">Andreas Fjorden Ree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan Thomas Jenssen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew Musgrave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Great Britain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gus Schumacher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pål Golberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friedrich Moch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iivo Niskanen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Lapalus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Davies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">William Poromaa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Ogden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naoto Baba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Japan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arsi Ruuskanen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathis Desloges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Even Northug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edvin Anger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federico Pellegrino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iver Tildheim Andersen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matz William Jenssen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Chanavat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Didrik Tønseth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florian Notz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aleksander Holmboe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mattis Stenshagen</t>
   </si>
   <si>
     <t xml:space="preserve">Erik Valnes</t>
   </si>
   <si>
-    <t xml:space="preserve">Federico Pellegrino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Italy</t>
+    <t xml:space="preserve">Irineu Esteve Altimiras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andorra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einar Hedegart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miha Simenc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovenia</t>
   </si>
   <si>
     <t xml:space="preserve">Mika Vermeulen</t>
@@ -65,445 +173,388 @@
     <t xml:space="preserve">Austria</t>
   </si>
   <si>
-    <t xml:space="preserve">Simen Hegstad Krüger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iivo Niskanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andreas Fjorden Ree</t>
+    <t xml:space="preserve">Nikolai Holmboe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truls Gisselman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jules Lapierre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valerio Grond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switzerland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benjamin Moser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Håvard Moseby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Håvard Solås Taugbøl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Hjalmar Westgård</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ireland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beda Klee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emil Danielsson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Janik Riebli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zanden McMullen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan Stoelben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alvar Johannes Alev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antoine Cyr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joni Mäki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remi Lindholm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oskar Opstad Vike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaume Pueyo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niilo Moilanen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anian Sossau</t>
   </si>
   <si>
     <t xml:space="preserve">Lauri Vuorinen</t>
   </si>
   <si>
-    <t xml:space="preserve">Pål Golberg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gus Schumacher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Friedrich Moch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zanden McMullen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arsi Ruuskanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mathis Desloges</t>
-  </si>
-  <si>
-    <t xml:space="preserve">France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Lapalus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan Thomas Jenssen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edvin Anger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweden</t>
+    <t xml:space="preserve">Andrew Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maciej Starega</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Albert Kuchler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Janosch Brugger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paolo Ventura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johan Häggström</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marius Kastner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nejc Stern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Fellner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czechia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eero Rantala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remi Bourdin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sander Haukvik-Jensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Hellweger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ansgar Evensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominik Bury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Linnebo Mollestad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calle Halfvarsson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ondrej Cerny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theo Schely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcus Grate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Hollmann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simone Dapra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alvar Myhlback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnus Øyaas Håbrekke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emil Liekari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johnny Hagenbuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivier Leveille</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haruki Yamashita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Clinton Schoonmaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martin Himma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryo Hirose</t>
   </si>
   <si>
     <t xml:space="preserve">Jules Chappaz</t>
   </si>
   <si>
-    <t xml:space="preserve">Even Northug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">William Poromaa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Hjalmar Westgård</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ireland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Halfvarsson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jens Burman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niilo Moilanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcus Grate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emil Iversen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benjamin Moser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jules Lapierre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oskar Opstad Vike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emil Danielsson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juuso Haarala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Theo Schely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Janik Riebli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switzerland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ville Ahonen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiljam Mattila</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valerio Grond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Albert Kuchler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emil Liekari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Davies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Great Britain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Irineu Esteve Altimiras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andorra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remi Lindholm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beda Klee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nejc Stern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Truls Gisselman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaume Pueyo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spain</t>
+    <t xml:space="preserve">Lauris Kaparkalejs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ole Tafjord Suhrke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qiang Wang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">China</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Clugnet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richard Jouve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sivert Wiig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyril Fähndrich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elia Barp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kevin Bolger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter Wonders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lauri Lepistö</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zak Ketterson</t>
   </si>
   <si>
     <t xml:space="preserve">Davide Graz</t>
   </si>
   <si>
-    <t xml:space="preserve">Florian Notz</t>
+    <t xml:space="preserve">Miha Licef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johan Ekberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renaud Jay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Büki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Konya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anton Grahn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anze Gros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bentley Walker-Broose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bernat Selles Gasch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daito Yamazaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francesco De Fabiani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fredrik Gerardo Fodstad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colombia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabriel Gledhill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imanol Rojo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan-Friedrich Doerks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ji-Yeong Byun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jiri Tuz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jong-Won Jeong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joon-Seo Lee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kamil Bury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lars Young Vik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Bögl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ludek Seller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marko Kilp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathias Holbæk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matyas Bauer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Earnhart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Måns Skoglund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nail Bashmakov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kazakhstan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niks Saulitis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oleksandr Lisohor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ukraine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olzhas Klimin</t>
   </si>
   <si>
     <t xml:space="preserve">Oskar Svensson</t>
   </si>
   <si>
-    <t xml:space="preserve">Ben Ogden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richard Jouve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyril Fähndrich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Föttinger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alvar Johannes Alev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan Stoelben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Janosch Brugger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Hellweger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bernat Selles Gasch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olivier Leveille</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zak Ketterson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sivert Wiig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Måns Skoglund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elia Barp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Håvard Solås Taugbøl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miha Simenc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antoine Cyr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remi Bourdin</t>
+    <t xml:space="preserve">Pierre Grall-Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sasha Masson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sebastian Kristoffer Endrestad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seve De Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simeon Deyanov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulgaria</t>
   </si>
   <si>
     <t xml:space="preserve">Svyatoslav Matassov</t>
   </si>
   <si>
-    <t xml:space="preserve">Kazakhstan</t>
+    <t xml:space="preserve">Tomas Dufek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitaliy Pukhkalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vladislav Kovalyov</t>
   </si>
   <si>
     <t xml:space="preserve">Xavier McKeever</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eero Rantala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ristomatti Hakola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martin Himma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johan Häggström</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Markus Vuorela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Hollmann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ike Melnits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anian Sossau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joni Mäki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lauri Lepistö</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ondrej Cerny</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czechia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johan Ekberg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas Chanavat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lauri Mannila</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ludek Seller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simone Dapra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hunter Wonders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas Bögl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matyas Bauer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paolo Ventura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomas Dufek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aleksi Parttimaa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Clinton Schoonmaker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Büki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Fellner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Konya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alexander Ståhlberg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrej Renda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovakia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bentley Walker-Broose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Australia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dmytro Drahun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ukraine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dmytro Romanchenko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fedor Karpov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francesco De Fabiani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gustav Kvarnbrink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Henri Roos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imanol Rojo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan-Friedrich Doerks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jiri Tuz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johnny Hagenbuch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juuso Varis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kevin Bolger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lauris Kaparkalejs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latvia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marko Kilp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Earnhart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miha Licef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mikayel Mikayelyan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miro Karppanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nail Bashmakov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oleksandr Lisohor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olzhas Klimin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pierre Grall-Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raimo Vigants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ralf Kivil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renaud Jay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandijs Suhanovs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sasha Masson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seve De Campo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simeon Deyanov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulgaria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spartak Voskanyan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veeti Pyykko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vladislav Kovalyov</t>
   </si>
   <si>
     <t xml:space="preserve">Yernar Nursbekov</t>
@@ -869,22 +920,22 @@
         <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>1716.28672156764</v>
+        <v>1777.62077009411</v>
       </c>
       <c r="D2" t="n">
-        <v>1777.62077009411</v>
+        <v>1862.67924993133</v>
       </c>
       <c r="E2" t="n">
-        <v>61.3340485264669</v>
+        <v>85.0584798372233</v>
       </c>
       <c r="F2" t="n">
         <v>232.355075344873</v>
       </c>
       <c r="G2" t="n">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="H2" t="n">
-        <v>0.644924655126999</v>
+        <v>23.644924655127</v>
       </c>
     </row>
     <row r="3">
@@ -895,22 +946,22 @@
         <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>1832.50248386365</v>
+        <v>1791.39005873349</v>
       </c>
       <c r="D3" t="n">
-        <v>1883.30442619851</v>
+        <v>1871.31237803244</v>
       </c>
       <c r="E3" t="n">
-        <v>50.8019423348583</v>
+        <v>79.9223192989548</v>
       </c>
       <c r="F3" t="n">
-        <v>196.313893302572</v>
+        <v>155.586768361572</v>
       </c>
       <c r="G3" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H3" t="n">
-        <v>-11.313893302572</v>
+        <v>34.413231638428</v>
       </c>
     </row>
     <row r="4">
@@ -921,22 +972,22 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>1683.85054850152</v>
+        <v>1732.63854535432</v>
       </c>
       <c r="D4" t="n">
-        <v>1791.39005873349</v>
+        <v>1827.27018594533</v>
       </c>
       <c r="E4" t="n">
-        <v>107.539510231969</v>
+        <v>94.631640591015</v>
       </c>
       <c r="F4" t="n">
-        <v>155.586768361572</v>
+        <v>171.486160244412</v>
       </c>
       <c r="G4" t="n">
         <v>180</v>
       </c>
       <c r="H4" t="n">
-        <v>24.413231638428</v>
+        <v>8.51383975558801</v>
       </c>
     </row>
     <row r="5">
@@ -947,22 +998,22 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>1681.64566939561</v>
+        <v>1883.30442619851</v>
       </c>
       <c r="D5" t="n">
-        <v>1782.84624176614</v>
+        <v>1904.39916131096</v>
       </c>
       <c r="E5" t="n">
-        <v>101.20057237053</v>
+        <v>21.0947351124478</v>
       </c>
       <c r="F5" t="n">
-        <v>143.638100570277</v>
+        <v>196.313893302572</v>
       </c>
       <c r="G5" t="n">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="H5" t="n">
-        <v>31.361899429723</v>
+        <v>-27.313893302572</v>
       </c>
     </row>
     <row r="6">
@@ -970,155 +1021,155 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>1593.27933940292</v>
+        <v>1620.85465888517</v>
       </c>
       <c r="D6" t="n">
-        <v>1650.18698088842</v>
+        <v>1743.87264485139</v>
       </c>
       <c r="E6" t="n">
-        <v>56.9076414855022</v>
+        <v>123.017985966217</v>
       </c>
       <c r="F6" t="n">
-        <v>167.499158663842</v>
+        <v>112.152044992285</v>
       </c>
       <c r="G6" t="n">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="H6" t="n">
-        <v>-5.499158663842</v>
+        <v>39.847955007715</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>1551.32846952439</v>
+        <v>1675.36303312098</v>
       </c>
       <c r="D7" t="n">
-        <v>1707.68147274823</v>
+        <v>1765.29600443506</v>
       </c>
       <c r="E7" t="n">
-        <v>156.353003223843</v>
+        <v>89.9329713140748</v>
       </c>
       <c r="F7" t="n">
-        <v>161.298329553994</v>
+        <v>146.5583294256</v>
       </c>
       <c r="G7" t="n">
         <v>151</v>
       </c>
       <c r="H7" t="n">
-        <v>-10.298329553994</v>
+        <v>4.44167057440001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>1613.90978856783</v>
+        <v>1468.28884241689</v>
       </c>
       <c r="D8" t="n">
-        <v>1732.63854535432</v>
+        <v>1666.97525860696</v>
       </c>
       <c r="E8" t="n">
-        <v>118.728756786486</v>
+        <v>198.686416190075</v>
       </c>
       <c r="F8" t="n">
-        <v>171.486160244412</v>
+        <v>107.188367574832</v>
       </c>
       <c r="G8" t="n">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="H8" t="n">
-        <v>-21.486160244412</v>
+        <v>27.811632425168</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
       <c r="C9" t="n">
-        <v>1627.91101768198</v>
+        <v>1658.55001448988</v>
       </c>
       <c r="D9" t="n">
-        <v>1574.9821296603</v>
+        <v>1657.34510148319</v>
       </c>
       <c r="E9" t="n">
-        <v>-52.9288880216832</v>
+        <v>-1.2049130066946</v>
       </c>
       <c r="F9" t="n">
-        <v>82.4593637227727</v>
+        <v>167.073229255693</v>
       </c>
       <c r="G9" t="n">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="H9" t="n">
-        <v>65.5406362772273</v>
+        <v>-35.073229255693</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>1315.83427890012</v>
+        <v>1714.55549720145</v>
       </c>
       <c r="D10" t="n">
-        <v>1620.85465888517</v>
+        <v>1756.42126087676</v>
       </c>
       <c r="E10" t="n">
-        <v>305.020379985056</v>
+        <v>41.8657636753062</v>
       </c>
       <c r="F10" t="n">
-        <v>112.152044992285</v>
+        <v>150.733754517878</v>
       </c>
       <c r="G10" t="n">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="H10" t="n">
-        <v>23.847955007715</v>
+        <v>-24.733754517878</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
         <v>21</v>
       </c>
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
       <c r="C11" t="n">
-        <v>1502.02153838739</v>
+        <v>1651.93742934766</v>
       </c>
       <c r="D11" t="n">
-        <v>1544.48561787577</v>
+        <v>1701.04599656446</v>
       </c>
       <c r="E11" t="n">
-        <v>42.4640794883821</v>
+        <v>49.1085672168033</v>
       </c>
       <c r="F11" t="n">
-        <v>71.8587077906508</v>
+        <v>134.378223010407</v>
       </c>
       <c r="G11" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H11" t="n">
-        <v>54.1412922093492</v>
+        <v>-14.378223010407</v>
       </c>
     </row>
     <row r="12">
@@ -1126,77 +1177,77 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
-        <v>1678.29988649939</v>
+        <v>1574.9821296603</v>
       </c>
       <c r="D12" t="n">
-        <v>1714.55549720145</v>
+        <v>1658.53002052194</v>
       </c>
       <c r="E12" t="n">
-        <v>36.255610702065</v>
+        <v>83.5478908616412</v>
       </c>
       <c r="F12" t="n">
-        <v>150.733754517878</v>
+        <v>82.4593637227727</v>
       </c>
       <c r="G12" t="n">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="H12" t="n">
-        <v>-32.733754517878</v>
+        <v>25.5406362772273</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" t="n">
-        <v>1549.18966600873</v>
+        <v>1443.99235308942</v>
       </c>
       <c r="D13" t="n">
-        <v>1658.55001448988</v>
+        <v>1610.76811022794</v>
       </c>
       <c r="E13" t="n">
-        <v>109.360348481154</v>
+        <v>166.775757138514</v>
       </c>
       <c r="F13" t="n">
-        <v>167.073229255693</v>
+        <v>68.9446271450143</v>
       </c>
       <c r="G13" t="n">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="H13" t="n">
-        <v>-52.073229255693</v>
+        <v>37.0553728549857</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>1537.68802492144</v>
+        <v>1461.93137931599</v>
       </c>
       <c r="D14" t="n">
-        <v>1651.93742934766</v>
+        <v>1603.14043560255</v>
       </c>
       <c r="E14" t="n">
-        <v>114.249404426221</v>
+        <v>141.20905628656</v>
       </c>
       <c r="F14" t="n">
-        <v>134.378223010407</v>
+        <v>59.3124253259264</v>
       </c>
       <c r="G14" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="H14" t="n">
-        <v>-20.378223010407</v>
+        <v>42.6875746740736</v>
       </c>
     </row>
     <row r="15">
@@ -1204,155 +1255,155 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>1432.58948009565</v>
+        <v>1599.38145958029</v>
       </c>
       <c r="D15" t="n">
-        <v>1577.14099996584</v>
+        <v>1661.33200756341</v>
       </c>
       <c r="E15" t="n">
-        <v>144.551519870196</v>
+        <v>61.9505479831164</v>
       </c>
       <c r="F15" t="n">
-        <v>103.663627435586</v>
+        <v>118.947254574374</v>
       </c>
       <c r="G15" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="H15" t="n">
-        <v>4.33637256441401</v>
+        <v>-16.947254574374</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>1390.26961386343</v>
+        <v>1490.95241863316</v>
       </c>
       <c r="D16" t="n">
-        <v>1578.58831147893</v>
+        <v>1552.10022866739</v>
       </c>
       <c r="E16" t="n">
-        <v>188.318697615501</v>
+        <v>61.1478100342304</v>
       </c>
       <c r="F16" t="n">
-        <v>47.7583062017317</v>
+        <v>118.173799200251</v>
       </c>
       <c r="G16" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H16" t="n">
-        <v>50.2416937982683</v>
+        <v>-18.173799200251</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C17" t="n">
-        <v>1312.20707817307</v>
+        <v>1415.55745145904</v>
       </c>
       <c r="D17" t="n">
-        <v>1565.03819652323</v>
+        <v>1579.27411741055</v>
       </c>
       <c r="E17" t="n">
-        <v>252.831118350166</v>
+        <v>163.716665951509</v>
       </c>
       <c r="F17" t="n">
-        <v>51.8592370756589</v>
+        <v>53.2217573702722</v>
       </c>
       <c r="G17" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H17" t="n">
-        <v>44.1407629243411</v>
+        <v>44.7782426297278</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>1503.88979947255</v>
+        <v>1578.58831147893</v>
       </c>
       <c r="D18" t="n">
-        <v>1443.99235308942</v>
+        <v>1628.4609909446</v>
       </c>
       <c r="E18" t="n">
-        <v>-59.8974463831291</v>
+        <v>49.8726794656718</v>
       </c>
       <c r="F18" t="n">
-        <v>68.9446271450143</v>
+        <v>47.7583062017317</v>
       </c>
       <c r="G18" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H18" t="n">
-        <v>26.0553728549857</v>
+        <v>48.2416937982683</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C19" t="n">
-        <v>1564.8679639741</v>
+        <v>1565.03819652323</v>
       </c>
       <c r="D19" t="n">
-        <v>1675.36303312098</v>
+        <v>1635.77506789625</v>
       </c>
       <c r="E19" t="n">
-        <v>110.495069146877</v>
+        <v>70.73687137302</v>
       </c>
       <c r="F19" t="n">
-        <v>146.5583294256</v>
+        <v>51.8592370756589</v>
       </c>
       <c r="G19" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H19" t="n">
-        <v>-51.5583294256</v>
+        <v>44.1407629243411</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>1497.65808858371</v>
+        <v>1706.24565100368</v>
       </c>
       <c r="D20" t="n">
-        <v>1599.27259176139</v>
+        <v>1764.49064843948</v>
       </c>
       <c r="E20" t="n">
-        <v>101.614503177675</v>
+        <v>58.2449974358008</v>
       </c>
       <c r="F20" t="n">
-        <v>104.738013997767</v>
+        <v>86.9965637582437</v>
       </c>
       <c r="G20" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H20" t="n">
-        <v>-10.738013997767</v>
+        <v>8.0034362417563</v>
       </c>
     </row>
     <row r="21">
@@ -1360,25 +1411,25 @@
         <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C21" t="n">
-        <v>1486.62548924242</v>
+        <v>1599.27259176139</v>
       </c>
       <c r="D21" t="n">
-        <v>1527.51687773613</v>
+        <v>1611.09008920874</v>
       </c>
       <c r="E21" t="n">
-        <v>40.8913884937101</v>
+        <v>11.8174974473579</v>
       </c>
       <c r="F21" t="n">
-        <v>49.0096055471202</v>
+        <v>104.738013997767</v>
       </c>
       <c r="G21" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H21" t="n">
-        <v>44.9903944528798</v>
+        <v>-14.738013997767</v>
       </c>
     </row>
     <row r="22">
@@ -1386,77 +1437,77 @@
         <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="C22" t="n">
-        <v>1641.86772126826</v>
+        <v>1650.18698088842</v>
       </c>
       <c r="D22" t="n">
-        <v>1706.24565100368</v>
+        <v>1580.71692422769</v>
       </c>
       <c r="E22" t="n">
-        <v>64.377929735417</v>
+        <v>-69.470056660728</v>
       </c>
       <c r="F22" t="n">
-        <v>86.9965637582437</v>
+        <v>167.499158663842</v>
       </c>
       <c r="G22" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.9965637582437</v>
+        <v>-77.499158663842</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C23" t="n">
-        <v>1539.40876582246</v>
+        <v>1520.46780805017</v>
       </c>
       <c r="D23" t="n">
-        <v>1599.38145958029</v>
+        <v>1649.53506617092</v>
       </c>
       <c r="E23" t="n">
-        <v>59.9726937578339</v>
+        <v>129.067258120759</v>
       </c>
       <c r="F23" t="n">
-        <v>118.947254574374</v>
+        <v>59.0014107425476</v>
       </c>
       <c r="G23" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H23" t="n">
-        <v>-34.947254574374</v>
+        <v>25.9985892574524</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C24" t="n">
-        <v>1346.35352691278</v>
+        <v>1380.37144608509</v>
       </c>
       <c r="D24" t="n">
-        <v>1483.02214933811</v>
+        <v>1559.88625158612</v>
       </c>
       <c r="E24" t="n">
-        <v>136.668622425322</v>
+        <v>179.514805501033</v>
       </c>
       <c r="F24" t="n">
-        <v>41.1814686333513</v>
+        <v>40.5884698428329</v>
       </c>
       <c r="G24" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H24" t="n">
-        <v>41.8185313666487</v>
+        <v>44.4115301571671</v>
       </c>
     </row>
     <row r="25">
@@ -1464,25 +1515,25 @@
         <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C25" t="n">
-        <v>1563.01858470824</v>
+        <v>1461.73267877583</v>
       </c>
       <c r="D25" t="n">
-        <v>1577.29506651728</v>
+        <v>1596.62890311743</v>
       </c>
       <c r="E25" t="n">
-        <v>14.2764818090438</v>
+        <v>134.896224341597</v>
       </c>
       <c r="F25" t="n">
-        <v>89.6220537514497</v>
+        <v>90.3243833929585</v>
       </c>
       <c r="G25" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H25" t="n">
-        <v>-7.6220537514497</v>
+        <v>-10.3243833929585</v>
       </c>
     </row>
     <row r="26">
@@ -1490,47 +1541,51 @@
         <v>41</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C26" t="n">
-        <v>1572.79896774971</v>
+        <v>1612.98910716473</v>
       </c>
       <c r="D26" t="n">
-        <v>1527.38186692716</v>
+        <v>1595.05066457213</v>
       </c>
       <c r="E26" t="n">
-        <v>-45.4171008225483</v>
-      </c>
-      <c r="F26"/>
+        <v>-17.9384425925937</v>
+      </c>
+      <c r="F26" t="n">
+        <v>137.314188387281</v>
+      </c>
       <c r="G26" t="n">
-        <v>80</v>
-      </c>
-      <c r="H26"/>
+        <v>78</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-59.314188387281</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
         <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C27" t="n">
-        <v>1432.64957310633</v>
+        <v>1510.82582883438</v>
       </c>
       <c r="D27" t="n">
-        <v>1574.77452580073</v>
+        <v>1567.28085904402</v>
       </c>
       <c r="E27" t="n">
-        <v>142.124952694398</v>
+        <v>56.4550302096395</v>
       </c>
       <c r="F27" t="n">
-        <v>24.2202085814252</v>
+        <v>73.0750064242733</v>
       </c>
       <c r="G27" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H27" t="n">
-        <v>55.7797914185748</v>
+        <v>2.9249935757267</v>
       </c>
     </row>
     <row r="28">
@@ -1538,25 +1593,25 @@
         <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C28" t="n">
-        <v>1489.18059176702</v>
+        <v>1315.85387296039</v>
       </c>
       <c r="D28" t="n">
-        <v>1601.24456456218</v>
+        <v>1517.86092283804</v>
       </c>
       <c r="E28" t="n">
-        <v>112.063972795161</v>
+        <v>202.007049877652</v>
       </c>
       <c r="F28" t="n">
-        <v>36.4626677565754</v>
+        <v>42.6434453048608</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
       </c>
       <c r="H28" t="n">
-        <v>38.5373322434246</v>
+        <v>32.3565546951392</v>
       </c>
     </row>
     <row r="29">
@@ -1567,1784 +1622,1796 @@
         <v>9</v>
       </c>
       <c r="C29" t="n">
-        <v>1497.00614302032</v>
+        <v>1522.19329543617</v>
       </c>
       <c r="D29" t="n">
-        <v>1489.89777522108</v>
+        <v>1640.48662254758</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.10836779924398</v>
-      </c>
-      <c r="F29"/>
+        <v>118.29332711141</v>
+      </c>
+      <c r="F29" t="n">
+        <v>50.2375035666487</v>
+      </c>
       <c r="G29" t="n">
-        <v>72</v>
-      </c>
-      <c r="H29"/>
+        <v>75</v>
+      </c>
+      <c r="H29" t="n">
+        <v>24.7624964333513</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
         <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C30" t="n">
-        <v>1331.98392441477</v>
+        <v>1782.84624176614</v>
       </c>
       <c r="D30" t="n">
-        <v>1505.69899524631</v>
+        <v>1797.80446892377</v>
       </c>
       <c r="E30" t="n">
-        <v>173.715070831539</v>
-      </c>
-      <c r="F30"/>
+        <v>14.9582271576292</v>
+      </c>
+      <c r="F30" t="n">
+        <v>143.638100570277</v>
+      </c>
       <c r="G30" t="n">
-        <v>69</v>
-      </c>
-      <c r="H30"/>
+        <v>72</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-71.638100570277</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
         <v>46</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C31" t="n">
-        <v>1504.6413120546</v>
+        <v>1488.95392278456</v>
       </c>
       <c r="D31" t="n">
-        <v>1553.8881079525</v>
+        <v>1546.32778825819</v>
       </c>
       <c r="E31" t="n">
-        <v>49.2467958979007</v>
+        <v>57.3738654736321</v>
       </c>
       <c r="F31" t="n">
-        <v>63.2523212658169</v>
+        <v>57.7639247589304</v>
       </c>
       <c r="G31" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H31" t="n">
-        <v>3.7476787341831</v>
+        <v>12.2360752410696</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
       </c>
       <c r="C32"/>
       <c r="D32" t="n">
-        <v>1483.42927742961</v>
+        <v>1513.07900933384</v>
       </c>
       <c r="E32"/>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.180580066145256</v>
       </c>
       <c r="G32" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H32" t="n">
-        <v>66</v>
+        <v>68.8194199338547</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C33" t="n">
-        <v>1399.50787480019</v>
+        <v>1370.44889139131</v>
       </c>
       <c r="D33" t="n">
-        <v>1531.84415229279</v>
+        <v>1493.17327758942</v>
       </c>
       <c r="E33" t="n">
-        <v>132.336277492604</v>
+        <v>122.724386198109</v>
       </c>
       <c r="F33" t="n">
-        <v>44.6561706580677</v>
+        <v>37.4852374826548</v>
       </c>
       <c r="G33" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H33" t="n">
-        <v>18.3438293419323</v>
+        <v>31.5147625173452</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="C34" t="n">
-        <v>1350.20382206372</v>
+        <v>1707.68147274823</v>
       </c>
       <c r="D34" t="n">
-        <v>1404.18663732454</v>
+        <v>1521.77033948389</v>
       </c>
       <c r="E34" t="n">
-        <v>53.9828152608202</v>
-      </c>
-      <c r="F34"/>
+        <v>-185.911133264343</v>
+      </c>
+      <c r="F34" t="n">
+        <v>161.298329553994</v>
+      </c>
       <c r="G34" t="n">
-        <v>63</v>
-      </c>
-      <c r="H34"/>
+        <v>69</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-92.298329553994</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C35" t="n">
-        <v>1442.35022614279</v>
+        <v>1291.97298844005</v>
       </c>
       <c r="D35" t="n">
-        <v>1448.04511869077</v>
+        <v>1485.9546305501</v>
       </c>
       <c r="E35" t="n">
-        <v>5.69489254798214</v>
-      </c>
-      <c r="F35" t="n">
-        <v>42.2473923637372</v>
-      </c>
+        <v>193.98164211005</v>
+      </c>
+      <c r="F35"/>
       <c r="G35" t="n">
-        <v>62</v>
-      </c>
-      <c r="H35" t="n">
-        <v>19.7526076362628</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="H35"/>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C36" t="n">
-        <v>1423.69737830464</v>
+        <v>1476.78610926328</v>
       </c>
       <c r="D36" t="n">
-        <v>1387.81849429878</v>
+        <v>1535.22571466071</v>
       </c>
       <c r="E36" t="n">
-        <v>-35.8788840058623</v>
-      </c>
-      <c r="F36"/>
+        <v>58.4396053974365</v>
+      </c>
+      <c r="F36" t="n">
+        <v>62.6776033838748</v>
+      </c>
       <c r="G36" t="n">
-        <v>58</v>
-      </c>
-      <c r="H36"/>
+        <v>63</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.322396616125197</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B37" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C37" t="n">
-        <v>1422.29325010824</v>
+        <v>1553.8881079525</v>
       </c>
       <c r="D37" t="n">
-        <v>1496.0268734711</v>
+        <v>1536.54403925726</v>
       </c>
       <c r="E37" t="n">
-        <v>73.73362336286</v>
-      </c>
-      <c r="F37"/>
+        <v>-17.3440686952415</v>
+      </c>
+      <c r="F37" t="n">
+        <v>63.2523212658169</v>
+      </c>
       <c r="G37" t="n">
-        <v>58</v>
-      </c>
-      <c r="H37"/>
+        <v>62</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-1.2523212658169</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B38" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="C38" t="n">
-        <v>1302.79820124923</v>
+        <v>1454.6072896059</v>
       </c>
       <c r="D38" t="n">
-        <v>1464.9500757303</v>
+        <v>1562.85594443174</v>
       </c>
       <c r="E38" t="n">
-        <v>162.151874481064</v>
+        <v>108.248654825838</v>
       </c>
       <c r="F38"/>
       <c r="G38" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H38"/>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B39" t="s">
         <v>52</v>
       </c>
       <c r="C39" t="n">
-        <v>1557.3486235048</v>
+        <v>1505.69899524631</v>
       </c>
       <c r="D39" t="n">
-        <v>1454.6072896059</v>
+        <v>1585.59443414039</v>
       </c>
       <c r="E39" t="n">
-        <v>-102.741333898898</v>
+        <v>79.8954388940833</v>
       </c>
       <c r="F39"/>
       <c r="G39" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H39"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>1334.96146793973</v>
+        <v>1488.19557902206</v>
       </c>
       <c r="D40" t="n">
-        <v>1397.5495748619</v>
+        <v>1562.95748611673</v>
       </c>
       <c r="E40" t="n">
-        <v>62.5881069221691</v>
+        <v>74.7619070946689</v>
       </c>
       <c r="F40" t="n">
-        <v>10.1482272767541</v>
+        <v>35.2981872472419</v>
       </c>
       <c r="G40" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H40" t="n">
-        <v>41.8517727232459</v>
+        <v>18.7018127527581</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C41" t="n">
-        <v>1387.38653305582</v>
+        <v>1542.20406414113</v>
       </c>
       <c r="D41" t="n">
-        <v>1427.509717627</v>
+        <v>1596.5252714533</v>
       </c>
       <c r="E41" t="n">
-        <v>40.1231845711809</v>
+        <v>54.3212073121756</v>
       </c>
       <c r="F41" t="n">
-        <v>6.6841121789931</v>
+        <v>79.027523589742</v>
       </c>
       <c r="G41" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H41" t="n">
-        <v>43.3158878210069</v>
+        <v>-25.027523589742</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C42" t="n">
-        <v>1329.34550893131</v>
+        <v>1483.02214933811</v>
       </c>
       <c r="D42" t="n">
-        <v>1461.93137931599</v>
+        <v>1463.87393453646</v>
       </c>
       <c r="E42" t="n">
-        <v>132.585870384679</v>
+        <v>-19.1482148016419</v>
       </c>
       <c r="F42" t="n">
-        <v>59.3124253259264</v>
+        <v>41.1814686333513</v>
       </c>
       <c r="G42" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H42" t="n">
-        <v>-9.3124253259264</v>
+        <v>12.8185313666487</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C43" t="n">
-        <v>1414.91122505</v>
+        <v>1387.37451112091</v>
       </c>
       <c r="D43" t="n">
-        <v>1488.95392278456</v>
+        <v>1480.19047357189</v>
       </c>
       <c r="E43" t="n">
-        <v>74.0426977345546</v>
+        <v>92.8159624509794</v>
       </c>
       <c r="F43" t="n">
-        <v>57.7639247589304</v>
+        <v>12.4600764573094</v>
       </c>
       <c r="G43" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H43" t="n">
-        <v>-8.7639247589304</v>
+        <v>40.5399235426906</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B44" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C44" t="n">
-        <v>1408.08391822413</v>
+        <v>1531.84415229279</v>
       </c>
       <c r="D44" t="n">
-        <v>1486.89601252553</v>
+        <v>1585.48133432789</v>
       </c>
       <c r="E44" t="n">
-        <v>78.8120943014032</v>
+        <v>53.6371820350989</v>
       </c>
       <c r="F44" t="n">
-        <v>37.2485307328134</v>
+        <v>44.6561706580677</v>
       </c>
       <c r="G44" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H44" t="n">
-        <v>11.7514692671866</v>
+        <v>7.3438293419323</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B45" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C45" t="n">
-        <v>1490.0914758717</v>
+        <v>1387.81849429878</v>
       </c>
       <c r="D45" t="n">
-        <v>1387.37451112091</v>
+        <v>1503.61230465594</v>
       </c>
       <c r="E45" t="n">
-        <v>-102.716964750796</v>
-      </c>
-      <c r="F45" t="n">
-        <v>12.4600764573094</v>
-      </c>
+        <v>115.793810357157</v>
+      </c>
+      <c r="F45"/>
       <c r="G45" t="n">
-        <v>48</v>
-      </c>
-      <c r="H45" t="n">
-        <v>35.5399235426906</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="H45"/>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="C46" t="n">
-        <v>1298.34760582355</v>
+        <v>1577.14099996584</v>
       </c>
       <c r="D46" t="n">
-        <v>1252.04920744048</v>
+        <v>1537.39849322354</v>
       </c>
       <c r="E46" t="n">
-        <v>-46.298398383067</v>
-      </c>
-      <c r="F46"/>
+        <v>-39.742506742298</v>
+      </c>
+      <c r="F46" t="n">
+        <v>103.663627435586</v>
+      </c>
       <c r="G46" t="n">
-        <v>48</v>
-      </c>
-      <c r="H46"/>
+        <v>49</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-54.663627435586</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C47" t="n">
-        <v>1378.77723324086</v>
+        <v>1354.99129627379</v>
       </c>
       <c r="D47" t="n">
-        <v>1476.78610926328</v>
+        <v>1402.95346906763</v>
       </c>
       <c r="E47" t="n">
-        <v>98.0088760224141</v>
+        <v>47.9621727938422</v>
       </c>
       <c r="F47" t="n">
-        <v>62.6776033838748</v>
+        <v>30.1720703121227</v>
       </c>
       <c r="G47" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>-14.6776033838748</v>
+        <v>15.8279296878773</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B48" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C48" t="n">
-        <v>1353.52694323441</v>
+        <v>1431.94544649883</v>
       </c>
       <c r="D48" t="n">
-        <v>1467.23580508058</v>
+        <v>1447.29119017389</v>
       </c>
       <c r="E48" t="n">
-        <v>113.708861846175</v>
-      </c>
-      <c r="F48"/>
+        <v>15.3457436750587</v>
+      </c>
+      <c r="F48" t="n">
+        <v>40.1160193738529</v>
+      </c>
       <c r="G48" t="n">
-        <v>46</v>
-      </c>
-      <c r="H48"/>
+        <v>44</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3.8839806261471</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B49" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="C49" t="n">
-        <v>1396.14664776737</v>
+        <v>1526.32909897701</v>
       </c>
       <c r="D49" t="n">
-        <v>1419.67807523692</v>
+        <v>1372.07480029912</v>
       </c>
       <c r="E49" t="n">
-        <v>23.5314274695545</v>
+        <v>-154.25429867789</v>
       </c>
       <c r="F49" t="n">
-        <v>68.5362730275637</v>
+        <v>87.303047531856</v>
       </c>
       <c r="G49" t="n">
         <v>44</v>
       </c>
       <c r="H49" t="n">
-        <v>-24.5362730275637</v>
+        <v>-43.303047531856</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B50" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C50" t="n">
-        <v>1421.15380744187</v>
+        <v>1392.82394946776</v>
       </c>
       <c r="D50" t="n">
-        <v>1510.82582883438</v>
+        <v>1491.12411812722</v>
       </c>
       <c r="E50" t="n">
-        <v>89.6720213925043</v>
+        <v>98.3001686594605</v>
       </c>
       <c r="F50" t="n">
-        <v>73.0750064242733</v>
+        <v>76.4294963860184</v>
       </c>
       <c r="G50" t="n">
         <v>44</v>
       </c>
       <c r="H50" t="n">
-        <v>-29.0750064242733</v>
+        <v>-32.4294963860184</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B51" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C51" t="n">
-        <v>1414.50046451123</v>
+        <v>1486.89601252553</v>
       </c>
       <c r="D51" t="n">
-        <v>1494.92261296351</v>
+        <v>1470.93258325945</v>
       </c>
       <c r="E51" t="n">
-        <v>80.4221484522818</v>
+        <v>-15.9634292660885</v>
       </c>
       <c r="F51" t="n">
-        <v>38.6483183455481</v>
+        <v>37.2485307328134</v>
       </c>
       <c r="G51" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H51" t="n">
-        <v>5.3516816544519</v>
+        <v>5.7514692671866</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B52" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C52" t="n">
-        <v>1533.84901324296</v>
+        <v>1483.42927742961</v>
       </c>
       <c r="D52" t="n">
-        <v>1490.95241863316</v>
+        <v>1533.29999753553</v>
       </c>
       <c r="E52" t="n">
-        <v>-42.8965946098001</v>
+        <v>49.8707201059203</v>
       </c>
       <c r="F52" t="n">
-        <v>118.173799200251</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H52" t="n">
-        <v>-75.173799200251</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B53" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="C53" t="n">
-        <v>1490.33006340119</v>
+        <v>1467.23580508058</v>
       </c>
       <c r="D53" t="n">
-        <v>1303.05941471845</v>
+        <v>1519.56245118207</v>
       </c>
       <c r="E53" t="n">
-        <v>-187.270648682735</v>
-      </c>
-      <c r="F53" t="n">
-        <v>30.8604749767171</v>
-      </c>
+        <v>52.326646101485</v>
+      </c>
+      <c r="F53"/>
       <c r="G53" t="n">
-        <v>43</v>
-      </c>
-      <c r="H53" t="n">
-        <v>12.1395250232829</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H53"/>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B54" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C54" t="n">
-        <v>1427.63351041191</v>
+        <v>1574.77452580073</v>
       </c>
       <c r="D54" t="n">
-        <v>1365.74931632287</v>
+        <v>1576.09674890641</v>
       </c>
       <c r="E54" t="n">
-        <v>-61.8841940890361</v>
+        <v>1.32222310568272</v>
       </c>
       <c r="F54" t="n">
-        <v>11.5579954343986</v>
+        <v>24.2202085814252</v>
       </c>
       <c r="G54" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H54" t="n">
-        <v>30.4420045656014</v>
+        <v>13.7797914185748</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B55" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C55" t="n">
-        <v>1305.40607036687</v>
+        <v>1366.42448967425</v>
       </c>
       <c r="D55" t="n">
-        <v>1431.36543949933</v>
+        <v>1429.89047636204</v>
       </c>
       <c r="E55" t="n">
-        <v>125.959369132461</v>
-      </c>
-      <c r="F55"/>
+        <v>63.4659866877905</v>
+      </c>
+      <c r="F55" t="n">
+        <v>43.8267258560375</v>
+      </c>
       <c r="G55" t="n">
-        <v>42</v>
-      </c>
-      <c r="H55"/>
+        <v>37</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-6.8267258560375</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B56" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="C56" t="n">
-        <v>1273.68085280555</v>
+        <v>1544.48561787577</v>
       </c>
       <c r="D56" t="n">
-        <v>1431.94544649883</v>
+        <v>1552.86780834892</v>
       </c>
       <c r="E56" t="n">
-        <v>158.264593693274</v>
+        <v>8.38219047315033</v>
       </c>
       <c r="F56" t="n">
-        <v>40.1160193738529</v>
+        <v>71.8587077906508</v>
       </c>
       <c r="G56" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.1160193738529</v>
+        <v>-35.8587077906508</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B57" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C57" t="n">
-        <v>1380.78817727288</v>
+        <v>1344.39624682369</v>
       </c>
       <c r="D57" t="n">
-        <v>1354.99129627379</v>
+        <v>1391.4916893482</v>
       </c>
       <c r="E57" t="n">
-        <v>-25.7968809990853</v>
+        <v>47.0954425245125</v>
       </c>
       <c r="F57" t="n">
-        <v>30.1720703121227</v>
+        <v>32.4301181207676</v>
       </c>
       <c r="G57" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H57" t="n">
-        <v>9.8279296878773</v>
+        <v>2.5698818792324</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B58" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="C58" t="n">
-        <v>1337.91966278106</v>
+        <v>1222.30544567165</v>
       </c>
       <c r="D58" t="n">
-        <v>1303.34059983774</v>
+        <v>1380.23374271839</v>
       </c>
       <c r="E58" t="n">
-        <v>-34.5790629433213</v>
-      </c>
-      <c r="F58" t="n">
-        <v>33.397564994679</v>
-      </c>
+        <v>157.92829704674</v>
+      </c>
+      <c r="F58"/>
       <c r="G58" t="n">
-        <v>40</v>
-      </c>
-      <c r="H58" t="n">
-        <v>6.602435005321</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="H58"/>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B59" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C59" t="n">
-        <v>1410.81093607715</v>
+        <v>1397.5495748619</v>
       </c>
       <c r="D59" t="n">
-        <v>1472.93023689294</v>
+        <v>1384.69026091955</v>
       </c>
       <c r="E59" t="n">
-        <v>62.1193008157925</v>
+        <v>-12.8593139423522</v>
       </c>
       <c r="F59" t="n">
-        <v>45.1440943708213</v>
+        <v>10.1482272767541</v>
       </c>
       <c r="G59" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H59" t="n">
-        <v>-9.1440943708213</v>
+        <v>22.8517727232459</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="C60" t="n">
-        <v>1289.19091005169</v>
+        <v>1303.34059983774</v>
       </c>
       <c r="D60" t="n">
-        <v>1402.53212048124</v>
+        <v>1375.42337571815</v>
       </c>
       <c r="E60" t="n">
-        <v>113.341210429558</v>
-      </c>
-      <c r="F60"/>
+        <v>72.0827758804123</v>
+      </c>
+      <c r="F60" t="n">
+        <v>33.397564994679</v>
+      </c>
       <c r="G60" t="n">
-        <v>34</v>
-      </c>
-      <c r="H60"/>
+        <v>33</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-0.397564994679001</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B61" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="C61" t="n">
-        <v>1302.71464070026</v>
+        <v>1310.14010394169</v>
       </c>
       <c r="D61" t="n">
-        <v>1369.46206024823</v>
+        <v>1420.02081287069</v>
       </c>
       <c r="E61" t="n">
-        <v>66.7474195479745</v>
-      </c>
-      <c r="F61" t="n">
-        <v>27.7527887621692</v>
-      </c>
+        <v>109.880708929002</v>
+      </c>
+      <c r="F61"/>
       <c r="G61" t="n">
-        <v>34</v>
-      </c>
-      <c r="H61" t="n">
-        <v>6.2472112378308</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="H61"/>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C62" t="n">
-        <v>1362.73372658313</v>
+        <v>1338.06814993215</v>
       </c>
       <c r="D62" t="n">
-        <v>1408.68179248636</v>
+        <v>1404.97092184453</v>
       </c>
       <c r="E62" t="n">
-        <v>45.948065903229</v>
+        <v>66.902771912379</v>
       </c>
       <c r="F62" t="n">
-        <v>23.8654198920702</v>
+        <v>9.10900240624349</v>
       </c>
       <c r="G62" t="n">
         <v>31</v>
       </c>
       <c r="H62" t="n">
-        <v>7.1345801079298</v>
+        <v>21.8909975937565</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B63" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C63" t="n">
-        <v>1460.24649266129</v>
+        <v>1460.91629483517</v>
       </c>
       <c r="D63" t="n">
-        <v>1484.96392199933</v>
+        <v>1417.78236540845</v>
       </c>
       <c r="E63" t="n">
-        <v>24.7174293380397</v>
+        <v>-43.1339294267198</v>
       </c>
       <c r="F63" t="n">
-        <v>31.0797379192388</v>
+        <v>70.0616793722097</v>
       </c>
       <c r="G63" t="n">
         <v>30</v>
       </c>
       <c r="H63" t="n">
-        <v>-1.0797379192388</v>
+        <v>-40.0616793722097</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B64" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C64" t="n">
-        <v>1317.83332915338</v>
+        <v>1355.7847328834</v>
       </c>
       <c r="D64" t="n">
-        <v>1402.70772552165</v>
+        <v>1437.65400878932</v>
       </c>
       <c r="E64" t="n">
-        <v>84.8743963682716</v>
-      </c>
-      <c r="F64" t="n">
-        <v>17.3666469183003</v>
-      </c>
+        <v>81.8692759059195</v>
+      </c>
+      <c r="F64"/>
       <c r="G64" t="n">
-        <v>29</v>
-      </c>
-      <c r="H64" t="n">
-        <v>11.6333530816997</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="H64"/>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B65" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="C65" t="n">
-        <v>1396.61826757244</v>
+        <v>1252.04920744048</v>
       </c>
       <c r="D65" t="n">
-        <v>1409.85603071411</v>
+        <v>1235.8612885841</v>
       </c>
       <c r="E65" t="n">
-        <v>13.2377631416784</v>
-      </c>
-      <c r="F65" t="n">
-        <v>52.8835809757905</v>
-      </c>
+        <v>-16.1879188563819</v>
+      </c>
+      <c r="F65"/>
       <c r="G65" t="n">
         <v>28</v>
       </c>
-      <c r="H65" t="n">
-        <v>-24.8835809757905</v>
-      </c>
+      <c r="H65"/>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B66" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="C66" t="n">
-        <v>1566.53148576821</v>
+        <v>1262.35359448273</v>
       </c>
       <c r="D66" t="n">
-        <v>1542.20406414113</v>
+        <v>1305.86928452641</v>
       </c>
       <c r="E66" t="n">
-        <v>-24.3274216270804</v>
+        <v>43.5156900436791</v>
       </c>
       <c r="F66" t="n">
-        <v>79.027523589742</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H66" t="n">
-        <v>-51.027523589742</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B67" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="C67" t="n">
-        <v>1288.58003561271</v>
+        <v>1377.23622152375</v>
       </c>
       <c r="D67" t="n">
-        <v>1370.44889139131</v>
+        <v>1438.32108598172</v>
       </c>
       <c r="E67" t="n">
-        <v>81.8688557786083</v>
+        <v>61.0848644579737</v>
       </c>
       <c r="F67" t="n">
-        <v>37.4852374826548</v>
+        <v>0.712276881366283</v>
       </c>
       <c r="G67" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H67" t="n">
-        <v>-9.4852374826548</v>
+        <v>25.2877231186337</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B68" t="s">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="C68" t="n">
-        <v>1532.31131537481</v>
+        <v>1330.68970725315</v>
       </c>
       <c r="D68" t="n">
-        <v>1526.32909897701</v>
+        <v>1346.03124644134</v>
       </c>
       <c r="E68" t="n">
-        <v>-5.98221639779808</v>
+        <v>15.3415391881922</v>
       </c>
       <c r="F68" t="n">
-        <v>87.303047531856</v>
+        <v>21.8633270685318</v>
       </c>
       <c r="G68" t="n">
         <v>26</v>
       </c>
       <c r="H68" t="n">
-        <v>-61.303047531856</v>
+        <v>4.1366729314682</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B69" t="s">
-        <v>30</v>
-      </c>
-      <c r="C69" t="n">
-        <v>1378.47290210806</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C69"/>
       <c r="D69" t="n">
-        <v>1330.68970725315</v>
-      </c>
-      <c r="E69" t="n">
-        <v>-47.7831948549126</v>
-      </c>
-      <c r="F69" t="n">
-        <v>21.8633270685318</v>
-      </c>
+        <v>1415.57900933384</v>
+      </c>
+      <c r="E69"/>
+      <c r="F69"/>
       <c r="G69" t="n">
-        <v>24</v>
-      </c>
-      <c r="H69" t="n">
-        <v>2.1366729314682</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H69"/>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B70" t="s">
-        <v>93</v>
+        <v>37</v>
       </c>
       <c r="C70" t="n">
-        <v>1243.26364664067</v>
+        <v>1472.93023689294</v>
       </c>
       <c r="D70" t="n">
-        <v>1351.96805217056</v>
+        <v>1482.61668613717</v>
       </c>
       <c r="E70" t="n">
-        <v>108.704405529894</v>
-      </c>
-      <c r="F70"/>
+        <v>9.68644924422915</v>
+      </c>
+      <c r="F70" t="n">
+        <v>45.1440943708213</v>
+      </c>
       <c r="G70" t="n">
         <v>24</v>
       </c>
-      <c r="H70"/>
+      <c r="H70" t="n">
+        <v>-21.1440943708213</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B71" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="C71" t="n">
-        <v>1287.75678661742</v>
+        <v>1370.80802998312</v>
       </c>
       <c r="D71" t="n">
-        <v>1340.43431183224</v>
+        <v>1415.11765668797</v>
       </c>
       <c r="E71" t="n">
-        <v>52.6775252148179</v>
+        <v>44.3096267048547</v>
       </c>
       <c r="F71" t="n">
-        <v>8.08525711019738</v>
+        <v>37.7337956672455</v>
       </c>
       <c r="G71" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H71" t="n">
-        <v>14.9147428898026</v>
+        <v>-18.7337956672455</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B72" t="s">
+        <v>82</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1246.49072154022</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1321.61212382949</v>
+      </c>
+      <c r="E72" t="n">
+        <v>75.1214022892764</v>
+      </c>
+      <c r="F72" t="n">
+        <v>3.96685704150533</v>
+      </c>
+      <c r="G72" t="n">
         <v>19</v>
       </c>
-      <c r="C72" t="n">
-        <v>1297.80778466446</v>
-      </c>
-      <c r="D72" t="n">
-        <v>1377.23622152375</v>
-      </c>
-      <c r="E72" t="n">
-        <v>79.428436859286</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0.712276881366283</v>
-      </c>
-      <c r="G72" t="n">
-        <v>22</v>
-      </c>
       <c r="H72" t="n">
-        <v>21.2877231186337</v>
+        <v>15.0331429584947</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B73" t="s">
-        <v>19</v>
-      </c>
-      <c r="C73" t="n">
-        <v>1450.2163741327</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C73"/>
       <c r="D73" t="n">
-        <v>1388.63223190762</v>
-      </c>
-      <c r="E73" t="n">
-        <v>-61.5841422250774</v>
-      </c>
+        <v>1355.74053177662</v>
+      </c>
+      <c r="E73"/>
       <c r="F73"/>
       <c r="G73" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H73"/>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B74" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="C74" t="n">
-        <v>1252.30662124607</v>
+        <v>1577.29506651728</v>
       </c>
       <c r="D74" t="n">
-        <v>1250.50302664765</v>
+        <v>1536.86939324964</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.80359459842452</v>
+        <v>-40.4256732676376</v>
       </c>
       <c r="F74" t="n">
-        <v>4.6456003228911</v>
+        <v>89.6220537514497</v>
       </c>
       <c r="G74" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H74" t="n">
-        <v>16.3543996771089</v>
+        <v>-71.6220537514497</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B75" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="C75" t="n">
-        <v>1461.95866475797</v>
+        <v>1436.71091721514</v>
       </c>
       <c r="D75" t="n">
-        <v>1460.91629483517</v>
+        <v>1438.49694484054</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.04236992280312</v>
+        <v>1.7860276254039</v>
       </c>
       <c r="F75" t="n">
-        <v>70.0616793722097</v>
+        <v>22.2973954045205</v>
       </c>
       <c r="G75" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H75" t="n">
-        <v>-50.0616793722097</v>
+        <v>-5.2973954045205</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B76" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C76" t="n">
-        <v>1392.2127035417</v>
+        <v>1448.04511869077</v>
       </c>
       <c r="D76" t="n">
-        <v>1380.59228861214</v>
+        <v>1354.73632327954</v>
       </c>
       <c r="E76" t="n">
-        <v>-11.6204149295575</v>
-      </c>
-      <c r="F76"/>
+        <v>-93.3087954112323</v>
+      </c>
+      <c r="F76" t="n">
+        <v>42.2473923637372</v>
+      </c>
       <c r="G76" t="n">
-        <v>19</v>
-      </c>
-      <c r="H76"/>
+        <v>17</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-25.2473923637372</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B77" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="C77" t="n">
-        <v>1269.52295657049</v>
+        <v>1601.24456456218</v>
       </c>
       <c r="D77" t="n">
-        <v>1372.47501781288</v>
+        <v>1527.66718216143</v>
       </c>
       <c r="E77" t="n">
-        <v>102.952061242399</v>
+        <v>-73.5773824007508</v>
       </c>
       <c r="F77" t="n">
-        <v>35.0326971645828</v>
+        <v>36.4626677565754</v>
       </c>
       <c r="G77" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H77" t="n">
-        <v>-16.0326971645828</v>
+        <v>-20.4626677565754</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B78" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="C78" t="n">
-        <v>1288.52761036301</v>
+        <v>1372.47501781288</v>
       </c>
       <c r="D78" t="n">
-        <v>1357.16899842654</v>
+        <v>1337.41468193884</v>
       </c>
       <c r="E78" t="n">
-        <v>68.6413880635339</v>
-      </c>
-      <c r="F78"/>
+        <v>-35.0603358740448</v>
+      </c>
+      <c r="F78" t="n">
+        <v>35.0326971645828</v>
+      </c>
       <c r="G78" t="n">
-        <v>18</v>
-      </c>
-      <c r="H78"/>
+        <v>16</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-19.0326971645828</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B79" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C79" t="n">
-        <v>1368.07683837586</v>
+        <v>1340.68225930938</v>
       </c>
       <c r="D79" t="n">
-        <v>1366.42448967425</v>
+        <v>1317.51685652719</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.65234870161089</v>
+        <v>-23.1654027821958</v>
       </c>
       <c r="F79" t="n">
-        <v>43.8267258560375</v>
+        <v>19.1895043107217</v>
       </c>
       <c r="G79" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H79" t="n">
-        <v>-26.8267258560375</v>
+        <v>-3.1895043107217</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B80" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C80" t="n">
-        <v>1518.86053219101</v>
+        <v>1326.00650025779</v>
       </c>
       <c r="D80" t="n">
-        <v>1392.82394946776</v>
+        <v>1317.50015473648</v>
       </c>
       <c r="E80" t="n">
-        <v>-126.036582723246</v>
+        <v>-8.50634552130418</v>
       </c>
       <c r="F80" t="n">
-        <v>76.4294963860184</v>
+        <v>13.8649603537588</v>
       </c>
       <c r="G80" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H80" t="n">
-        <v>-59.4294963860184</v>
+        <v>0.1350396462412</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B81" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C81" t="n">
-        <v>1345.4500130994</v>
+        <v>1301.88367675187</v>
       </c>
       <c r="D81" t="n">
-        <v>1396.7864210423</v>
+        <v>1355.90820737183</v>
       </c>
       <c r="E81" t="n">
-        <v>51.3364079429005</v>
+        <v>54.0245306199599</v>
       </c>
       <c r="F81" t="n">
-        <v>15.1687870129419</v>
+        <v>8.43859016753701</v>
       </c>
       <c r="G81" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H81" t="n">
-        <v>1.8312129870581</v>
+        <v>5.56140983246299</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B82" t="s">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="C82" t="n">
-        <v>1445.31643095792</v>
+        <v>1427.509717627</v>
       </c>
       <c r="D82" t="n">
-        <v>1436.71091721514</v>
+        <v>1413.74459855484</v>
       </c>
       <c r="E82" t="n">
-        <v>-8.60551374278157</v>
+        <v>-13.7651190721679</v>
       </c>
       <c r="F82" t="n">
-        <v>22.2973954045205</v>
+        <v>6.6841121789931</v>
       </c>
       <c r="G82" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H82" t="n">
-        <v>-5.2973954045205</v>
+        <v>6.3158878210069</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B83" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C83" t="n">
-        <v>1305.25506662218</v>
+        <v>1172.18030834246</v>
       </c>
       <c r="D83" t="n">
-        <v>1366.07113361029</v>
+        <v>1228.09873859409</v>
       </c>
       <c r="E83" t="n">
-        <v>60.8160669881104</v>
+        <v>55.9184302516298</v>
       </c>
       <c r="F83" t="n">
-        <v>12.0327401802724</v>
+        <v>5.6106371396872</v>
       </c>
       <c r="G83" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H83" t="n">
-        <v>2.9672598197276</v>
+        <v>7.3893628603128</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B84" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="C84" t="n">
-        <v>1524.48619676264</v>
+        <v>1369.46206024823</v>
       </c>
       <c r="D84" t="n">
-        <v>1461.73267877583</v>
+        <v>1301.12820764629</v>
       </c>
       <c r="E84" t="n">
-        <v>-62.7535179868132</v>
+        <v>-68.3338526019406</v>
       </c>
       <c r="F84" t="n">
-        <v>90.3243833929585</v>
+        <v>27.7527887621692</v>
       </c>
       <c r="G84" t="n">
         <v>13</v>
       </c>
       <c r="H84" t="n">
-        <v>-77.3243833929585</v>
+        <v>-14.7527887621692</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B85" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C85" t="n">
-        <v>1341.21690240996</v>
+        <v>1269.89946894169</v>
       </c>
       <c r="D85" t="n">
-        <v>1288.16055970987</v>
+        <v>1245.21964888208</v>
       </c>
       <c r="E85" t="n">
-        <v>-53.056342700087</v>
-      </c>
-      <c r="F85"/>
+        <v>-24.6798200596104</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2.34513385898218</v>
+      </c>
       <c r="G85" t="n">
-        <v>11</v>
-      </c>
-      <c r="H85"/>
+        <v>12</v>
+      </c>
+      <c r="H85" t="n">
+        <v>9.65486614101782</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B86" t="s">
-        <v>106</v>
+        <v>18</v>
       </c>
       <c r="C86" t="n">
-        <v>1401.52613134349</v>
+        <v>1394.14561845328</v>
       </c>
       <c r="D86" t="n">
-        <v>1377.92910693935</v>
+        <v>1391.78843557895</v>
       </c>
       <c r="E86" t="n">
-        <v>-23.5970244041407</v>
+        <v>-2.35718287433247</v>
       </c>
       <c r="F86" t="n">
-        <v>21.5532029610601</v>
+        <v>54.9860717062536</v>
       </c>
       <c r="G86" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H86" t="n">
-        <v>-11.5532029610601</v>
+        <v>-42.9860717062536</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B87" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="C87" t="n">
-        <v>1397.98015517541</v>
+        <v>1250.50302664765</v>
       </c>
       <c r="D87" t="n">
-        <v>1340.68225930938</v>
+        <v>1287.14292535744</v>
       </c>
       <c r="E87" t="n">
-        <v>-57.2978958660303</v>
+        <v>36.6398987097948</v>
       </c>
       <c r="F87" t="n">
-        <v>19.1895043107217</v>
+        <v>4.6456003228911</v>
       </c>
       <c r="G87" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H87" t="n">
-        <v>-9.1895043107217</v>
+        <v>7.3543996771089</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B88" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C88" t="n">
-        <v>1344.98821503156</v>
+        <v>1310.30932291344</v>
       </c>
       <c r="D88" t="n">
-        <v>1336.22200453655</v>
+        <v>1314.98961278297</v>
       </c>
       <c r="E88" t="n">
-        <v>-8.76621049500477</v>
+        <v>4.68028986952709</v>
       </c>
       <c r="F88" t="n">
-        <v>10.5656096839533</v>
+        <v>13.0558258530677</v>
       </c>
       <c r="G88" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H88" t="n">
-        <v>-1.5656096839533</v>
+        <v>-1.0558258530677</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B89" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C89" t="n">
-        <v>1360.69880986186</v>
+        <v>1527.51687773613</v>
       </c>
       <c r="D89" t="n">
-        <v>1322.83271314644</v>
+        <v>1375.20323340953</v>
       </c>
       <c r="E89" t="n">
-        <v>-37.8660967154281</v>
-      </c>
-      <c r="F89"/>
+        <v>-152.313644326599</v>
+      </c>
+      <c r="F89" t="n">
+        <v>49.0096055471202</v>
+      </c>
       <c r="G89" t="n">
-        <v>8</v>
-      </c>
-      <c r="H89"/>
+        <v>11</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-38.0096055471202</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B90" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C90" t="n">
-        <v>1263.6141587878</v>
+        <v>968.388356752684</v>
       </c>
       <c r="D90" t="n">
-        <v>1192.01214066638</v>
+        <v>1030.51167671307</v>
       </c>
       <c r="E90" t="n">
-        <v>-71.6020181214185</v>
+        <v>62.1233199603834</v>
       </c>
       <c r="F90" t="n">
-        <v>5.89320422551477</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H90" t="n">
-        <v>1.10679577448523</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B91" t="s">
-        <v>14</v>
-      </c>
-      <c r="C91" t="n">
-        <v>1374.59823295431</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C91"/>
       <c r="D91" t="n">
-        <v>1338.06814993215</v>
-      </c>
-      <c r="E91" t="n">
-        <v>-36.5300830221595</v>
-      </c>
+        <v>1355.57900933384</v>
+      </c>
+      <c r="E91"/>
       <c r="F91" t="n">
-        <v>9.10900240624349</v>
+        <v>0.180580066145256</v>
       </c>
       <c r="G91" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H91" t="n">
-        <v>-2.10900240624349</v>
+        <v>10.8194199338547</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B92" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C92" t="n">
-        <v>1239.90933271401</v>
+        <v>1416.09760966892</v>
       </c>
       <c r="D92" t="n">
-        <v>1182.85330503783</v>
+        <v>1392.89995964446</v>
       </c>
       <c r="E92" t="n">
-        <v>-57.0560276761785</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
+        <v>-23.197650024463</v>
+      </c>
+      <c r="F92"/>
       <c r="G92" t="n">
-        <v>6</v>
-      </c>
-      <c r="H92" t="n">
-        <v>6</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H92"/>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B93" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C93" t="n">
-        <v>1286.34618546485</v>
+        <v>1349.9075803003</v>
       </c>
       <c r="D93" t="n">
-        <v>1296.2264826223</v>
+        <v>1354.74021302423</v>
       </c>
       <c r="E93" t="n">
-        <v>9.88029715745188</v>
+        <v>4.83263272392378</v>
       </c>
       <c r="F93"/>
       <c r="G93" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H93"/>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B94" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C94" t="n">
-        <v>1511.5632336453</v>
+        <v>1303.05941471845</v>
       </c>
       <c r="D94" t="n">
-        <v>1394.14561845328</v>
+        <v>1326.49456361991</v>
       </c>
       <c r="E94" t="n">
-        <v>-117.417615192015</v>
+        <v>23.4351489014548</v>
       </c>
       <c r="F94" t="n">
-        <v>54.9860717062536</v>
+        <v>30.8604749767171</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H94" t="n">
-        <v>-53.9860717062536</v>
+        <v>-22.8604749767171</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B95" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="C95" t="n">
-        <v>1160.83610544738</v>
+        <v>1484.96392199933</v>
       </c>
       <c r="D95" t="n">
-        <v>925.377686472707</v>
+        <v>1414.13657707039</v>
       </c>
       <c r="E95" t="n">
-        <v>-235.458418974673</v>
+        <v>-70.8273449289359</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>31.0797379192388</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>-24.0797379192388</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B96" t="s">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="C96" t="n">
-        <v>1292.91073000204</v>
+        <v>1365.74931632287</v>
       </c>
       <c r="D96" t="n">
-        <v>1262.35359448273</v>
+        <v>1283.87966506942</v>
       </c>
       <c r="E96" t="n">
-        <v>-30.557135519314</v>
+        <v>-81.8696512534539</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>11.5579954343986</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>-5.5579954343986</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B97" t="s">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="C97" t="n">
-        <v>1093.45768422727</v>
+        <v>1409.85603071411</v>
       </c>
       <c r="D97" t="n">
-        <v>924.286265636509</v>
+        <v>1307.88844969493</v>
       </c>
       <c r="E97" t="n">
-        <v>-169.171418590764</v>
+        <v>-101.967581019189</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>52.8835809757905</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>-46.8835809757905</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B98" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C98" t="n">
-        <v>1291.50213602643</v>
+        <v>1247.03993367731</v>
       </c>
       <c r="D98" t="n">
-        <v>1284.35701231604</v>
+        <v>1288.14155351861</v>
       </c>
       <c r="E98" t="n">
-        <v>-7.14512371038927</v>
+        <v>41.101619841299</v>
       </c>
       <c r="F98"/>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H98"/>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B99" t="s">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="C99" t="n">
-        <v>1134.61622117855</v>
+        <v>1336.22200453655</v>
       </c>
       <c r="D99" t="n">
-        <v>987.928572986164</v>
+        <v>1291.43220237474</v>
       </c>
       <c r="E99" t="n">
-        <v>-146.687648192381</v>
-      </c>
-      <c r="F99"/>
+        <v>-44.7898021618093</v>
+      </c>
+      <c r="F99" t="n">
+        <v>10.5656096839533</v>
+      </c>
       <c r="G99" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99"/>
+        <v>5</v>
+      </c>
+      <c r="H99" t="n">
+        <v>-5.5656096839533</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B100" t="s">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="C100" t="n">
-        <v>1157.31926232675</v>
+        <v>1396.7864210423</v>
       </c>
       <c r="D100" t="n">
-        <v>1011.00472144808</v>
+        <v>1309.06824716084</v>
       </c>
       <c r="E100" t="n">
-        <v>-146.31454087867</v>
+        <v>-87.7181738814554</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>15.1687870129419</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>-10.1687870129419</v>
       </c>
     </row>
     <row r="101">
@@ -3352,156 +3419,172 @@
         <v>128</v>
       </c>
       <c r="B101" t="s">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="C101" t="n">
-        <v>1138.67565316572</v>
+        <v>1408.68179248636</v>
       </c>
       <c r="D101" t="n">
-        <v>1079.97180831567</v>
+        <v>1280.06700380664</v>
       </c>
       <c r="E101" t="n">
-        <v>-58.7038448500489</v>
-      </c>
-      <c r="F101"/>
+        <v>-128.614788679716</v>
+      </c>
+      <c r="F101" t="n">
+        <v>23.8654198920702</v>
+      </c>
       <c r="G101" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101"/>
+        <v>4</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-19.8654198920702</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B102" t="s">
-        <v>129</v>
+        <v>37</v>
       </c>
       <c r="C102" t="n">
-        <v>1268.70349210129</v>
+        <v>1419.67807523692</v>
       </c>
       <c r="D102" t="n">
-        <v>1029.77381459779</v>
+        <v>1295.65520089837</v>
       </c>
       <c r="E102" t="n">
-        <v>-238.929677503499</v>
-      </c>
-      <c r="F102"/>
+        <v>-124.022874338554</v>
+      </c>
+      <c r="F102" t="n">
+        <v>68.5362730275637</v>
+      </c>
       <c r="G102" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102"/>
+        <v>3</v>
+      </c>
+      <c r="H102" t="n">
+        <v>-65.5362730275637</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B103" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="C103" t="n">
-        <v>1145.37442534721</v>
+        <v>1180.38168019195</v>
       </c>
       <c r="D103" t="n">
-        <v>1039.30347524601</v>
+        <v>1219.52709920621</v>
       </c>
       <c r="E103" t="n">
-        <v>-106.070950101205</v>
+        <v>39.1454190142595</v>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>1.79582733639708</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>1.20417266360292</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B104" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C104" t="n">
-        <v>1419.33557953915</v>
+        <v>1366.07113361029</v>
       </c>
       <c r="D104" t="n">
-        <v>1238.68357696276</v>
+        <v>1344.21641358691</v>
       </c>
       <c r="E104" t="n">
-        <v>-180.652002576393</v>
+        <v>-21.8547200233756</v>
       </c>
       <c r="F104" t="n">
-        <v>42.3578033388694</v>
+        <v>12.0327401802724</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H104" t="n">
-        <v>-42.3578033388694</v>
+        <v>-10.0327401802724</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B105" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C105" t="n">
-        <v>1276.94163869283</v>
+        <v>1341.47754203798</v>
       </c>
       <c r="D105" t="n">
-        <v>1287.34251820634</v>
+        <v>1315.56367637913</v>
       </c>
       <c r="E105" t="n">
-        <v>10.4008795135098</v>
-      </c>
-      <c r="F105"/>
+        <v>-25.9138656588475</v>
+      </c>
+      <c r="F105" t="n">
+        <v>63.2535705336811</v>
+      </c>
       <c r="G105" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105"/>
+        <v>2</v>
+      </c>
+      <c r="H105" t="n">
+        <v>-61.2535705336811</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
+        <v>133</v>
+      </c>
+      <c r="B106" t="s">
         <v>134</v>
       </c>
-      <c r="B106" t="s">
-        <v>77</v>
-      </c>
       <c r="C106" t="n">
-        <v>1206.82245938275</v>
+        <v>925.377686472707</v>
       </c>
       <c r="D106" t="n">
-        <v>1154.93651221347</v>
+        <v>811.295469662161</v>
       </c>
       <c r="E106" t="n">
-        <v>-51.8859471692801</v>
-      </c>
-      <c r="F106"/>
+        <v>-114.082216810546</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
-      <c r="H106"/>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
         <v>135</v>
       </c>
       <c r="B107" t="s">
-        <v>68</v>
+        <v>134</v>
       </c>
       <c r="C107" t="n">
-        <v>1242.10022278692</v>
+        <v>924.286265636509</v>
       </c>
       <c r="D107" t="n">
-        <v>1149.72931996421</v>
+        <v>853.578972199229</v>
       </c>
       <c r="E107" t="n">
-        <v>-92.3709028227058</v>
+        <v>-70.7072934372799</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
@@ -3518,87 +3601,91 @@
         <v>136</v>
       </c>
       <c r="B108" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C108" t="n">
-        <v>1319.47793305678</v>
+        <v>1322.91026926434</v>
       </c>
       <c r="D108" t="n">
-        <v>1182.50597080498</v>
+        <v>1256.36321792366</v>
       </c>
       <c r="E108" t="n">
-        <v>-136.971962251798</v>
-      </c>
-      <c r="F108"/>
+        <v>-66.5470513406876</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
-      <c r="H108"/>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
         <v>137</v>
       </c>
       <c r="B109" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="C109" t="n">
-        <v>1244.58270843847</v>
+        <v>1154.66142202063</v>
       </c>
       <c r="D109" t="n">
-        <v>1229.43669488403</v>
+        <v>1148.11082303068</v>
       </c>
       <c r="E109" t="n">
-        <v>-15.1460135544337</v>
-      </c>
-      <c r="F109" t="n">
-        <v>2.2677988275976</v>
-      </c>
+        <v>-6.55059898995</v>
+      </c>
+      <c r="F109"/>
       <c r="G109" t="n">
         <v>0</v>
       </c>
-      <c r="H109" t="n">
-        <v>-2.2677988275976</v>
-      </c>
+      <c r="H109"/>
     </row>
     <row r="110">
       <c r="A110" t="s">
         <v>138</v>
       </c>
       <c r="B110" t="s">
-        <v>24</v>
+        <v>139</v>
       </c>
       <c r="C110" t="n">
-        <v>1326.7624261308</v>
+        <v>1011.00472144808</v>
       </c>
       <c r="D110" t="n">
-        <v>1172.18030834246</v>
+        <v>931.615520569353</v>
       </c>
       <c r="E110" t="n">
-        <v>-154.582117788336</v>
+        <v>-79.3892008787299</v>
       </c>
       <c r="F110" t="n">
-        <v>5.6106371396872</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>-5.6106371396872</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B111" t="s">
-        <v>19</v>
-      </c>
-      <c r="C111"/>
+        <v>76</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1402.53212048124</v>
+      </c>
       <c r="D111" t="n">
-        <v>1179.43809557316</v>
-      </c>
-      <c r="E111"/>
+        <v>1266.01529701757</v>
+      </c>
+      <c r="E111" t="n">
+        <v>-136.516823463679</v>
+      </c>
       <c r="F111"/>
       <c r="G111" t="n">
         <v>0</v>
@@ -3607,20 +3694,16 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B112" t="s">
-        <v>24</v>
-      </c>
-      <c r="C112" t="n">
-        <v>1353.16058580607</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="C112"/>
       <c r="D112" t="n">
-        <v>1247.03993367731</v>
-      </c>
-      <c r="E112" t="n">
-        <v>-106.120652128753</v>
-      </c>
+        <v>1176.35055233677</v>
+      </c>
+      <c r="E112"/>
       <c r="F112"/>
       <c r="G112" t="n">
         <v>0</v>
@@ -3629,28 +3712,28 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B113" t="s">
-        <v>142</v>
+        <v>37</v>
       </c>
       <c r="C113" t="n">
-        <v>1186.95164820369</v>
+        <v>1238.68357696276</v>
       </c>
       <c r="D113" t="n">
-        <v>968.388356752684</v>
+        <v>1148.81368085929</v>
       </c>
       <c r="E113" t="n">
-        <v>-218.563291451004</v>
+        <v>-89.8698961034695</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>42.3578033388694</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>-42.3578033388694</v>
       </c>
     </row>
     <row r="114">
@@ -3658,94 +3741,90 @@
         <v>143</v>
       </c>
       <c r="B114" t="s">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="C114" t="n">
-        <v>1324.27772217134</v>
+        <v>1182.92773915851</v>
       </c>
       <c r="D114" t="n">
-        <v>1264.0577049974</v>
+        <v>995.118839215157</v>
       </c>
       <c r="E114" t="n">
-        <v>-60.2200171739407</v>
-      </c>
-      <c r="F114" t="n">
-        <v>8.96245266238689</v>
-      </c>
+        <v>-187.808899943357</v>
+      </c>
+      <c r="F114"/>
       <c r="G114" t="n">
         <v>0</v>
       </c>
-      <c r="H114" t="n">
-        <v>-8.96245266238689</v>
-      </c>
+      <c r="H114"/>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B115" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C115" t="n">
-        <v>1224.06136147372</v>
+        <v>1265.4709498096</v>
       </c>
       <c r="D115" t="n">
-        <v>1193.44846605539</v>
+        <v>1121.22078282836</v>
       </c>
       <c r="E115" t="n">
-        <v>-30.6128954183318</v>
+        <v>-144.250166981241</v>
       </c>
       <c r="F115" t="n">
-        <v>0.180479164220706</v>
+        <v>0.180580066145256</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>-0.180479164220706</v>
+        <v>-0.180580066145256</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B116" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C116" t="n">
-        <v>1217.41122309849</v>
+        <v>1149.72931996421</v>
       </c>
       <c r="D116" t="n">
-        <v>1180.38168019195</v>
+        <v>1173.46861108944</v>
       </c>
       <c r="E116" t="n">
-        <v>-37.0295429065409</v>
+        <v>23.7392911252311</v>
       </c>
       <c r="F116" t="n">
-        <v>1.79582733639708</v>
+        <v>0</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>-1.79582733639708</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B117" t="s">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="C117" t="n">
-        <v>1202.53686363419</v>
+        <v>1182.50597080498</v>
       </c>
       <c r="D117" t="n">
-        <v>1055.15796870094</v>
+        <v>1115.13702636695</v>
       </c>
       <c r="E117" t="n">
-        <v>-147.37889493325</v>
+        <v>-67.36894443803</v>
       </c>
       <c r="F117"/>
       <c r="G117" t="n">
@@ -3758,64 +3837,68 @@
         <v>148</v>
       </c>
       <c r="B118" t="s">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="C118" t="n">
-        <v>1289.87767936628</v>
+        <v>1232.3216056837</v>
       </c>
       <c r="D118" t="n">
-        <v>1238.07194293591</v>
+        <v>1045.82253134195</v>
       </c>
       <c r="E118" t="n">
-        <v>-51.8057364303684</v>
-      </c>
-      <c r="F118"/>
+        <v>-186.499074341747</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
       <c r="G118" t="n">
         <v>0</v>
       </c>
-      <c r="H118"/>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B119" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C119" t="n">
-        <v>1179.99757028175</v>
+        <v>1229.43669488403</v>
       </c>
       <c r="D119" t="n">
-        <v>1132.36678677561</v>
+        <v>1118.70769641305</v>
       </c>
       <c r="E119" t="n">
-        <v>-47.6307835061359</v>
+        <v>-110.728998470985</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>2.2677988275976</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>-2.2677988275976</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B120" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="C120" t="n">
-        <v>1126.38741464418</v>
+        <v>1109.53189836091</v>
       </c>
       <c r="D120" t="n">
-        <v>1091.63798998153</v>
+        <v>1032.62270805704</v>
       </c>
       <c r="E120" t="n">
-        <v>-34.7494246626568</v>
+        <v>-76.9091903038693</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
@@ -3829,45 +3912,37 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B121" t="s">
-        <v>93</v>
-      </c>
-      <c r="C121" t="n">
-        <v>1137.76769687829</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="C121"/>
       <c r="D121" t="n">
-        <v>1079.8915053622</v>
-      </c>
-      <c r="E121" t="n">
-        <v>-57.8761915160951</v>
-      </c>
-      <c r="F121" t="n">
-        <v>0</v>
-      </c>
+        <v>1039.47173415257</v>
+      </c>
+      <c r="E121"/>
+      <c r="F121"/>
       <c r="G121" t="n">
         <v>0</v>
       </c>
-      <c r="H121" t="n">
-        <v>0</v>
-      </c>
+      <c r="H121"/>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B122" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C122" t="n">
-        <v>1273.91417523984</v>
+        <v>1215.4933484064</v>
       </c>
       <c r="D122" t="n">
-        <v>1236.62830525907</v>
+        <v>1146.62384429582</v>
       </c>
       <c r="E122" t="n">
-        <v>-37.2858699807723</v>
+        <v>-68.8695041105734</v>
       </c>
       <c r="F122"/>
       <c r="G122" t="n">
@@ -3877,41 +3952,45 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B123" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C123" t="n">
-        <v>1188.81736327261</v>
+        <v>1197.52077057742</v>
       </c>
       <c r="D123" t="n">
-        <v>1075.4921978934</v>
+        <v>1113.99730077904</v>
       </c>
       <c r="E123" t="n">
-        <v>-113.325165379211</v>
-      </c>
-      <c r="F123"/>
+        <v>-83.5234697983717</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
-      <c r="H123"/>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B124" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="C124" t="n">
-        <v>1279.2318422115</v>
+        <v>1322.83271314644</v>
       </c>
       <c r="D124" t="n">
-        <v>1135.35377172119</v>
+        <v>1274.98402391646</v>
       </c>
       <c r="E124" t="n">
-        <v>-143.878070490309</v>
+        <v>-47.8486892299754</v>
       </c>
       <c r="F124"/>
       <c r="G124" t="n">
@@ -3921,63 +4000,71 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B125" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="C125" t="n">
-        <v>1453.95936905874</v>
+        <v>1377.92910693935</v>
       </c>
       <c r="D125" t="n">
-        <v>1341.47754203798</v>
+        <v>1273.66682254388</v>
       </c>
       <c r="E125" t="n">
-        <v>-112.48182702076</v>
+        <v>-104.262284395474</v>
       </c>
       <c r="F125" t="n">
-        <v>63.2535705336811</v>
+        <v>21.5532029610601</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>-63.2535705336811</v>
+        <v>-21.5532029610601</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B126" t="s">
-        <v>142</v>
-      </c>
-      <c r="C126"/>
+        <v>69</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1264.0577049974</v>
+      </c>
       <c r="D126" t="n">
-        <v>970.70476095813</v>
-      </c>
-      <c r="E126"/>
-      <c r="F126"/>
+        <v>1256.8638053978</v>
+      </c>
+      <c r="E126" t="n">
+        <v>-7.19389959960245</v>
+      </c>
+      <c r="F126" t="n">
+        <v>8.96245266238689</v>
+      </c>
       <c r="G126" t="n">
         <v>0</v>
       </c>
-      <c r="H126"/>
+      <c r="H126" t="n">
+        <v>-8.96245266238689</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B127" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="C127" t="n">
-        <v>1256.15402084873</v>
+        <v>1290.41158424394</v>
       </c>
       <c r="D127" t="n">
-        <v>1174.19928817103</v>
+        <v>1239.73198614374</v>
       </c>
       <c r="E127" t="n">
-        <v>-81.9547326776949</v>
+        <v>-50.6795981001997</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
@@ -3991,54 +4078,54 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B128" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="C128" t="n">
-        <v>1081.13147092793</v>
+        <v>1192.01214066638</v>
       </c>
       <c r="D128" t="n">
-        <v>1086.12968038345</v>
+        <v>1081.41529353228</v>
       </c>
       <c r="E128" t="n">
-        <v>4.99820945552233</v>
+        <v>-110.5968471341</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>5.89320422551477</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>-5.89320422551477</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B129" t="s">
-        <v>160</v>
+        <v>18</v>
       </c>
       <c r="C129" t="n">
-        <v>1129.60743466563</v>
+        <v>1193.44846605539</v>
       </c>
       <c r="D129" t="n">
-        <v>1154.95989374502</v>
+        <v>1221.29434970171</v>
       </c>
       <c r="E129" t="n">
-        <v>25.3524590793859</v>
+        <v>27.8458836463228</v>
       </c>
       <c r="F129" t="n">
-        <v>4.35177311608452</v>
+        <v>0.180479164220706</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>-4.35177311608452</v>
+        <v>-0.180479164220706</v>
       </c>
     </row>
     <row r="130">
@@ -4046,84 +4133,422 @@
         <v>161</v>
       </c>
       <c r="B130" t="s">
-        <v>147</v>
+        <v>28</v>
       </c>
       <c r="C130" t="n">
-        <v>1179.47126322372</v>
+        <v>1402.70772552165</v>
       </c>
       <c r="D130" t="n">
-        <v>964.0500254764</v>
+        <v>1322.7440506331</v>
       </c>
       <c r="E130" t="n">
-        <v>-215.421237747316</v>
-      </c>
-      <c r="F130"/>
+        <v>-79.9636748885571</v>
+      </c>
+      <c r="F130" t="n">
+        <v>17.3666469183003</v>
+      </c>
       <c r="G130" t="n">
         <v>0</v>
       </c>
-      <c r="H130"/>
+      <c r="H130" t="n">
+        <v>-17.3666469183003</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
         <v>162</v>
       </c>
       <c r="B131" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="C131" t="n">
-        <v>1276.66918343295</v>
+        <v>1132.36678677561</v>
       </c>
       <c r="D131" t="n">
-        <v>1246.15111059497</v>
+        <v>1076.14967123078</v>
       </c>
       <c r="E131" t="n">
-        <v>-30.5180728379803</v>
-      </c>
-      <c r="F131"/>
+        <v>-56.217115544833</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
-      <c r="H131"/>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B132" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="C132" t="n">
-        <v>1089.98827405841</v>
+        <v>1118.8537541534</v>
       </c>
       <c r="D132" t="n">
-        <v>1015.71318036304</v>
+        <v>942.652129805212</v>
       </c>
       <c r="E132" t="n">
-        <v>-74.2750936953631</v>
-      </c>
-      <c r="F132"/>
+        <v>-176.201624348193</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
-      <c r="H132"/>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B133" t="s">
-        <v>93</v>
-      </c>
-      <c r="C133"/>
+        <v>166</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1091.63798998153</v>
+      </c>
       <c r="D133" t="n">
+        <v>1074.64890591608</v>
+      </c>
+      <c r="E133" t="n">
+        <v>-16.9890840654518</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>167</v>
+      </c>
+      <c r="B134" t="s">
+        <v>163</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1079.8915053622</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1083.94460958575</v>
+      </c>
+      <c r="E134" t="n">
+        <v>4.05310422355501</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>168</v>
+      </c>
+      <c r="B135" t="s">
+        <v>28</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1494.92261296351</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1379.60301120477</v>
+      </c>
+      <c r="E135" t="n">
+        <v>-115.319601758741</v>
+      </c>
+      <c r="F135" t="n">
+        <v>38.6483183455481</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-38.6483183455481</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>169</v>
+      </c>
+      <c r="B136" t="s">
+        <v>71</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1236.62830525907</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1217.74428357864</v>
+      </c>
+      <c r="E136" t="n">
+        <v>-18.8840216804265</v>
+      </c>
+      <c r="F136"/>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>170</v>
+      </c>
+      <c r="B137" t="s">
+        <v>71</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1174.19928817103</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1148.68427480731</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-25.5150133637233</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>171</v>
+      </c>
+      <c r="B138" t="s">
+        <v>172</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1142.85494825832</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1026.30615642741</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-116.548791830912</v>
+      </c>
+      <c r="F138"/>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>173</v>
+      </c>
+      <c r="B139" t="s">
+        <v>139</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1086.12968038345</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1023.15072002493</v>
+      </c>
+      <c r="E139" t="n">
+        <v>-62.9789603585224</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>174</v>
+      </c>
+      <c r="B140" t="s">
+        <v>175</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1154.95989374502</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1026.72413479928</v>
+      </c>
+      <c r="E140" t="n">
+        <v>-128.235758945732</v>
+      </c>
+      <c r="F140" t="n">
+        <v>4.35177311608452</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>-4.35177311608452</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>176</v>
+      </c>
+      <c r="B141" t="s">
+        <v>163</v>
+      </c>
+      <c r="C141" t="n">
+        <v>1351.96805217056</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1225.76150054133</v>
+      </c>
+      <c r="E141" t="n">
+        <v>-126.206551629226</v>
+      </c>
+      <c r="F141"/>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>177</v>
+      </c>
+      <c r="B142" t="s">
+        <v>91</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1182.85330503783</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1068.89672650999</v>
+      </c>
+      <c r="E142" t="n">
+        <v>-113.956578527842</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>178</v>
+      </c>
+      <c r="B143" t="s">
+        <v>163</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1295.31305121596</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1198.15619163035</v>
+      </c>
+      <c r="E143" t="n">
+        <v>-97.1568595856093</v>
+      </c>
+      <c r="F143" t="n">
+        <v>3.09215875913276</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>-3.09215875913276</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>179</v>
+      </c>
+      <c r="B144" t="s">
+        <v>163</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1015.71318036304</v>
+      </c>
+      <c r="D144" t="n">
+        <v>996.212408337815</v>
+      </c>
+      <c r="E144" t="n">
+        <v>-19.5007720252273</v>
+      </c>
+      <c r="F144"/>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>180</v>
+      </c>
+      <c r="B145" t="s">
+        <v>71</v>
+      </c>
+      <c r="C145" t="n">
+        <v>1340.43431183224</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1185.56452736187</v>
+      </c>
+      <c r="E145" t="n">
+        <v>-154.869784470367</v>
+      </c>
+      <c r="F145" t="n">
+        <v>8.08525711019738</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>-8.08525711019738</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>181</v>
+      </c>
+      <c r="B146" t="s">
+        <v>163</v>
+      </c>
+      <c r="C146" t="n">
         <v>1134.97303969003</v>
       </c>
-      <c r="E133"/>
-      <c r="F133"/>
-      <c r="G133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133"/>
+      <c r="D146" t="n">
+        <v>1036.70373652157</v>
+      </c>
+      <c r="E146" t="n">
+        <v>-98.2693031684635</v>
+      </c>
+      <c r="F146"/>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
